--- a/output/graficos_nacionales/plot_nacional_regiones_i_peringrmin_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_peringrmin_a_2023.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 19:29</t>
+    <t xml:space="preserve">2026-08-20 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_peringrmin_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_peringrmin_a_2023.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 21:35</t>
+    <t xml:space="preserve">2026-08-21 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_peringrmin_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_peringrmin_a_2023.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 12:38</t>
+    <t xml:space="preserve">2026-09-07 12:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
